--- a/data/images/literature/reference_x/dimensions.xlsx
+++ b/data/images/literature/reference_x/dimensions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>PP</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Img microns</t>
+  </si>
+  <si>
+    <t>Laura</t>
   </si>
 </sst>
 </file>
@@ -354,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -398,7 +401,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <f>D2/C2*E2</f>
+        <f t="shared" ref="F2:F12" si="0">D2/C2*E2</f>
         <v>33.78531073446328</v>
       </c>
     </row>
@@ -419,7 +422,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <f>D3/C3*E3</f>
+        <f t="shared" si="0"/>
         <v>33.78531073446328</v>
       </c>
     </row>
@@ -440,7 +443,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <f>D4/C4*E4</f>
+        <f t="shared" si="0"/>
         <v>104.62882096069869</v>
       </c>
     </row>
@@ -461,7 +464,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <f>D5/C5*E5</f>
+        <f t="shared" si="0"/>
         <v>113.01886792452831</v>
       </c>
     </row>
@@ -482,7 +485,7 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <f>D6/C6*E6</f>
+        <f t="shared" si="0"/>
         <v>118.02955665024632</v>
       </c>
     </row>
@@ -503,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <f>D7/C7*E7</f>
+        <f t="shared" si="0"/>
         <v>118.02955665024632</v>
       </c>
     </row>
@@ -524,7 +527,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <f>D8/C8*E8</f>
+        <f t="shared" si="0"/>
         <v>119.49748743718594</v>
       </c>
     </row>
@@ -545,7 +548,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <f>D9/C9*E9</f>
+        <f t="shared" si="0"/>
         <v>38.688524590163937</v>
       </c>
     </row>
@@ -566,8 +569,34 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <f>D10/C10*E10</f>
+        <f t="shared" si="0"/>
         <v>39.022801302931597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>1.69</v>
+      </c>
+      <c r="D12">
+        <v>11.12</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>131.59763313609466</v>
       </c>
     </row>
   </sheetData>
